--- a/Sep_2026/daily Reports/Price List Custom.xlsx
+++ b/Sep_2026/daily Reports/Price List Custom.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4133A09-6A47-46A0-9387-DC661B5B1D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D93535D-8460-48A1-B4F2-4447FB0A03A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="948" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3399,6 +3399,75 @@
     <xf numFmtId="43" fontId="29" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3411,81 +3480,51 @@
     <xf numFmtId="0" fontId="34" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -3495,44 +3534,17 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3543,34 +3555,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="43" fontId="29" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -12021,24 +12021,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21 16383:16383" x14ac:dyDescent="0.35">
-      <c r="E1" s="311" t="s">
+      <c r="E1" s="334" t="s">
         <v>495</v>
       </c>
-      <c r="F1" s="311"/>
-      <c r="G1" s="311"/>
-      <c r="H1" s="311"/>
-      <c r="I1" s="311"/>
-      <c r="J1" s="311"/>
-      <c r="K1" s="311"/>
+      <c r="F1" s="334"/>
+      <c r="G1" s="334"/>
+      <c r="H1" s="334"/>
+      <c r="I1" s="334"/>
+      <c r="J1" s="334"/>
+      <c r="K1" s="334"/>
     </row>
     <row r="2" spans="1:21 16383:16383" x14ac:dyDescent="0.35">
-      <c r="E2" s="311"/>
-      <c r="F2" s="311"/>
-      <c r="G2" s="311"/>
-      <c r="H2" s="311"/>
-      <c r="I2" s="311"/>
-      <c r="J2" s="311"/>
-      <c r="K2" s="311"/>
+      <c r="E2" s="334"/>
+      <c r="F2" s="334"/>
+      <c r="G2" s="334"/>
+      <c r="H2" s="334"/>
+      <c r="I2" s="334"/>
+      <c r="J2" s="334"/>
+      <c r="K2" s="334"/>
     </row>
     <row r="3" spans="1:21 16383:16383" s="87" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="269" t="s">
@@ -12053,16 +12053,16 @@
       </c>
       <c r="F3" s="85"/>
       <c r="G3" s="86"/>
-      <c r="K3" s="310" t="s">
+      <c r="K3" s="333" t="s">
         <v>48</v>
       </c>
-      <c r="L3" s="310"/>
-      <c r="M3" s="310"/>
-      <c r="N3" s="309" t="s">
+      <c r="L3" s="333"/>
+      <c r="M3" s="333"/>
+      <c r="N3" s="332" t="s">
         <v>49</v>
       </c>
-      <c r="O3" s="309"/>
-      <c r="P3" s="309"/>
+      <c r="O3" s="332"/>
+      <c r="P3" s="332"/>
       <c r="Q3" s="85"/>
       <c r="R3" s="265"/>
       <c r="S3" s="266"/>
@@ -12081,14 +12081,14 @@
       </c>
       <c r="F4" s="85"/>
       <c r="G4" s="1"/>
-      <c r="K4" s="310" t="s">
+      <c r="K4" s="333" t="s">
         <v>50</v>
       </c>
-      <c r="L4" s="310"/>
-      <c r="M4" s="310"/>
-      <c r="N4" s="308"/>
-      <c r="O4" s="308"/>
-      <c r="P4" s="308"/>
+      <c r="L4" s="333"/>
+      <c r="M4" s="333"/>
+      <c r="N4" s="331"/>
+      <c r="O4" s="331"/>
+      <c r="P4" s="331"/>
       <c r="Q4" s="85"/>
       <c r="R4" s="264"/>
       <c r="XFC4" t="s">
@@ -12104,36 +12104,36 @@
       </c>
     </row>
     <row r="6" spans="1:21 16383:16383" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="329" t="s">
+      <c r="A6" s="308" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="329"/>
-      <c r="C6" s="329" t="s">
+      <c r="B6" s="308"/>
+      <c r="C6" s="308" t="s">
         <v>90</v>
       </c>
       <c r="D6" s="274" t="s">
         <v>52</v>
       </c>
-      <c r="E6" s="329" t="s">
+      <c r="E6" s="308" t="s">
         <v>58</v>
       </c>
-      <c r="F6" s="329"/>
-      <c r="G6" s="329" t="s">
+      <c r="F6" s="308"/>
+      <c r="G6" s="308" t="s">
         <v>54</v>
       </c>
-      <c r="H6" s="329"/>
-      <c r="I6" s="329" t="s">
+      <c r="H6" s="308"/>
+      <c r="I6" s="308" t="s">
         <v>77</v>
       </c>
-      <c r="J6" s="329" t="s">
+      <c r="J6" s="308" t="s">
         <v>55</v>
       </c>
-      <c r="K6" s="329"/>
-      <c r="L6" s="329"/>
-      <c r="M6" s="329" t="s">
+      <c r="K6" s="308"/>
+      <c r="L6" s="308"/>
+      <c r="M6" s="308" t="s">
         <v>84</v>
       </c>
-      <c r="N6" s="334" t="s">
+      <c r="N6" s="312" t="s">
         <v>494</v>
       </c>
       <c r="O6" s="274" t="s">
@@ -12147,9 +12147,9 @@
       </c>
     </row>
     <row r="7" spans="1:21 16383:16383" ht="20" x14ac:dyDescent="0.35">
-      <c r="A7" s="329"/>
-      <c r="B7" s="329"/>
-      <c r="C7" s="329"/>
+      <c r="A7" s="308"/>
+      <c r="B7" s="308"/>
+      <c r="C7" s="308"/>
       <c r="D7" s="274" t="s">
         <v>57</v>
       </c>
@@ -12165,9 +12165,9 @@
       <c r="H7" s="274" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="329"/>
+      <c r="I7" s="308"/>
       <c r="J7" s="275">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="K7" s="274" t="s">
         <v>39</v>
@@ -12175,8 +12175,8 @@
       <c r="L7" s="274" t="s">
         <v>492</v>
       </c>
-      <c r="M7" s="329"/>
-      <c r="N7" s="329"/>
+      <c r="M7" s="308"/>
+      <c r="N7" s="308"/>
       <c r="O7" s="276">
         <f>IF(B3="Filer",0.5%,2.5%)</f>
         <v>5.0000000000000001E-3</v>
@@ -12226,7 +12226,7 @@
       </c>
       <c r="J8" s="128">
         <f>I8*J7</f>
-        <v>209.85000000000002</v>
+        <v>167.88</v>
       </c>
       <c r="K8" s="128">
         <f>$I8*3.5%</f>
@@ -12238,7 +12238,7 @@
       </c>
       <c r="M8" s="213">
         <f>I8-SUM(J8:L8)</f>
-        <v>1815.2024999999999</v>
+        <v>1857.1725000000001</v>
       </c>
       <c r="N8" s="128">
         <f>+(G8*D8+H8)*9.92</f>
@@ -12246,11 +12246,11 @@
       </c>
       <c r="O8" s="128">
         <f t="shared" ref="O8:O14" si="1">(N8+M8)*$O$7</f>
-        <v>11.060012500000001</v>
+        <v>11.269862500000002</v>
       </c>
       <c r="P8" s="128">
         <f>M8+N8+O8</f>
-        <v>2223.0625125000001</v>
+        <v>2265.2423625000001</v>
       </c>
       <c r="R8" s="216"/>
       <c r="S8" s="247"/>
@@ -12423,7 +12423,7 @@
       </c>
       <c r="J11" s="128">
         <f>I11*J7</f>
-        <v>290.56</v>
+        <v>232.44800000000001</v>
       </c>
       <c r="K11" s="128">
         <f t="shared" si="3"/>
@@ -12435,7 +12435,7 @@
       </c>
       <c r="M11" s="213">
         <f t="shared" si="4"/>
-        <v>2513.3440000000001</v>
+        <v>2571.4560000000001</v>
       </c>
       <c r="N11" s="128">
         <f>+(G11*D11+H11)*13.73</f>
@@ -12443,11 +12443,11 @@
       </c>
       <c r="O11" s="128">
         <f t="shared" si="1"/>
-        <v>15.312719999999999</v>
+        <v>15.60328</v>
       </c>
       <c r="P11" s="128">
         <f t="shared" si="6"/>
-        <v>3077.8567199999998</v>
+        <v>3136.2592799999998</v>
       </c>
       <c r="R11" s="267"/>
       <c r="S11" s="268"/>
@@ -12646,17 +12646,17 @@
       <c r="U14" s="142"/>
     </row>
     <row r="15" spans="1:21 16383:16383" x14ac:dyDescent="0.35">
-      <c r="A15" s="326">
+      <c r="A15" s="311">
         <f>COUNT(A8:A14)</f>
         <v>0</v>
       </c>
-      <c r="B15" s="326"/>
-      <c r="C15" s="326" t="s">
+      <c r="B15" s="311"/>
+      <c r="C15" s="311" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="326"/>
-      <c r="E15" s="326"/>
-      <c r="F15" s="326"/>
+      <c r="D15" s="311"/>
+      <c r="E15" s="311"/>
+      <c r="F15" s="311"/>
       <c r="G15" s="281">
         <f t="shared" ref="G15:P15" si="9">SUM(G8:G14)</f>
         <v>3</v>
@@ -12671,7 +12671,7 @@
       </c>
       <c r="J15" s="282">
         <f t="shared" si="9"/>
-        <v>578.87</v>
+        <v>478.78800000000001</v>
       </c>
       <c r="K15" s="282">
         <f t="shared" si="9"/>
@@ -12683,7 +12683,7 @@
       </c>
       <c r="M15" s="281">
         <f t="shared" si="9"/>
-        <v>5684.3353000000006</v>
+        <v>5784.417300000001</v>
       </c>
       <c r="N15" s="281">
         <f t="shared" si="9"/>
@@ -12691,11 +12691,11 @@
       </c>
       <c r="O15" s="283">
         <f t="shared" si="9"/>
-        <v>34.677676500000004</v>
+        <v>35.178086500000006</v>
       </c>
       <c r="P15" s="281">
         <f t="shared" si="9"/>
-        <v>6970.2129765000009</v>
+        <v>7070.7953864999999</v>
       </c>
     </row>
     <row r="16" spans="1:21 16383:16383" x14ac:dyDescent="0.35">
@@ -12726,104 +12726,104 @@
       <c r="H17" s="94"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B18" s="316" t="s">
+      <c r="B18" s="317" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="317"/>
-      <c r="D18" s="317"/>
-      <c r="E18" s="317"/>
-      <c r="F18" s="317"/>
-      <c r="G18" s="317"/>
-      <c r="H18" s="317"/>
-      <c r="I18" s="317"/>
-      <c r="J18" s="317"/>
-      <c r="K18" s="317"/>
-      <c r="L18" s="318"/>
-      <c r="N18" s="330" t="s">
+      <c r="C18" s="318"/>
+      <c r="D18" s="318"/>
+      <c r="E18" s="318"/>
+      <c r="F18" s="318"/>
+      <c r="G18" s="318"/>
+      <c r="H18" s="318"/>
+      <c r="I18" s="318"/>
+      <c r="J18" s="318"/>
+      <c r="K18" s="318"/>
+      <c r="L18" s="319"/>
+      <c r="N18" s="309" t="s">
         <v>60</v>
       </c>
-      <c r="O18" s="331"/>
+      <c r="O18" s="310"/>
       <c r="P18" s="139">
         <f>I15</f>
         <v>6573.3000000000011</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="319"/>
-      <c r="C19" s="320"/>
-      <c r="D19" s="320"/>
-      <c r="E19" s="320"/>
-      <c r="F19" s="320"/>
-      <c r="G19" s="320"/>
-      <c r="H19" s="320"/>
-      <c r="I19" s="320"/>
-      <c r="J19" s="320"/>
-      <c r="K19" s="320"/>
-      <c r="L19" s="321"/>
-      <c r="N19" s="325" t="s">
+      <c r="B19" s="320"/>
+      <c r="C19" s="321"/>
+      <c r="D19" s="321"/>
+      <c r="E19" s="321"/>
+      <c r="F19" s="321"/>
+      <c r="G19" s="321"/>
+      <c r="H19" s="321"/>
+      <c r="I19" s="321"/>
+      <c r="J19" s="321"/>
+      <c r="K19" s="321"/>
+      <c r="L19" s="322"/>
+      <c r="N19" s="326" t="s">
         <v>85</v>
       </c>
-      <c r="O19" s="326"/>
+      <c r="O19" s="311"/>
       <c r="P19" s="140">
         <f>+J15</f>
-        <v>578.87</v>
+        <v>478.78800000000001</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="319"/>
-      <c r="C20" s="320"/>
-      <c r="D20" s="320"/>
-      <c r="E20" s="320"/>
-      <c r="F20" s="320"/>
-      <c r="G20" s="320"/>
-      <c r="H20" s="320"/>
-      <c r="I20" s="320"/>
-      <c r="J20" s="320"/>
-      <c r="K20" s="320"/>
-      <c r="L20" s="321"/>
-      <c r="N20" s="325" t="s">
+      <c r="B20" s="320"/>
+      <c r="C20" s="321"/>
+      <c r="D20" s="321"/>
+      <c r="E20" s="321"/>
+      <c r="F20" s="321"/>
+      <c r="G20" s="321"/>
+      <c r="H20" s="321"/>
+      <c r="I20" s="321"/>
+      <c r="J20" s="321"/>
+      <c r="K20" s="321"/>
+      <c r="L20" s="322"/>
+      <c r="N20" s="326" t="s">
         <v>86</v>
       </c>
-      <c r="O20" s="326"/>
+      <c r="O20" s="311"/>
       <c r="P20" s="140">
         <f>+K15+L15</f>
         <v>310.09470000000005</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="319"/>
-      <c r="C21" s="320"/>
-      <c r="D21" s="320"/>
-      <c r="E21" s="320"/>
-      <c r="F21" s="320"/>
-      <c r="G21" s="320"/>
-      <c r="H21" s="320"/>
-      <c r="I21" s="320"/>
-      <c r="J21" s="320"/>
-      <c r="K21" s="320"/>
-      <c r="L21" s="321"/>
+      <c r="B21" s="320"/>
+      <c r="C21" s="321"/>
+      <c r="D21" s="321"/>
+      <c r="E21" s="321"/>
+      <c r="F21" s="321"/>
+      <c r="G21" s="321"/>
+      <c r="H21" s="321"/>
+      <c r="I21" s="321"/>
+      <c r="J21" s="321"/>
+      <c r="K21" s="321"/>
+      <c r="L21" s="322"/>
       <c r="M21" s="131"/>
-      <c r="N21" s="325" t="s">
+      <c r="N21" s="326" t="s">
         <v>87</v>
       </c>
-      <c r="O21" s="326"/>
+      <c r="O21" s="311"/>
       <c r="P21" s="140">
         <f>P18-P19-P20</f>
-        <v>5684.3353000000016</v>
+        <v>5784.417300000001</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="319"/>
-      <c r="C22" s="320"/>
-      <c r="D22" s="320"/>
-      <c r="E22" s="320"/>
-      <c r="F22" s="320"/>
-      <c r="G22" s="320"/>
-      <c r="H22" s="320"/>
-      <c r="I22" s="320"/>
-      <c r="J22" s="320"/>
-      <c r="K22" s="320"/>
-      <c r="L22" s="321"/>
+      <c r="B22" s="320"/>
+      <c r="C22" s="321"/>
+      <c r="D22" s="321"/>
+      <c r="E22" s="321"/>
+      <c r="F22" s="321"/>
+      <c r="G22" s="321"/>
+      <c r="H22" s="321"/>
+      <c r="I22" s="321"/>
+      <c r="J22" s="321"/>
+      <c r="K22" s="321"/>
+      <c r="L22" s="322"/>
       <c r="M22" s="131"/>
       <c r="N22" s="136" t="s">
         <v>61</v>
@@ -12837,39 +12837,39 @@
       </c>
     </row>
     <row r="23" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="319"/>
-      <c r="C23" s="320"/>
-      <c r="D23" s="320"/>
-      <c r="E23" s="320"/>
-      <c r="F23" s="320"/>
-      <c r="G23" s="320"/>
-      <c r="H23" s="320"/>
-      <c r="I23" s="320"/>
-      <c r="J23" s="320"/>
-      <c r="K23" s="320"/>
-      <c r="L23" s="321"/>
+      <c r="B23" s="320"/>
+      <c r="C23" s="321"/>
+      <c r="D23" s="321"/>
+      <c r="E23" s="321"/>
+      <c r="F23" s="321"/>
+      <c r="G23" s="321"/>
+      <c r="H23" s="321"/>
+      <c r="I23" s="321"/>
+      <c r="J23" s="321"/>
+      <c r="K23" s="321"/>
+      <c r="L23" s="322"/>
       <c r="M23" s="131"/>
-      <c r="N23" s="332" t="s">
+      <c r="N23" s="329" t="s">
         <v>76</v>
       </c>
-      <c r="O23" s="333"/>
+      <c r="O23" s="330"/>
       <c r="P23" s="140">
         <f>P21+P22</f>
-        <v>6935.5353000000014</v>
+        <v>7035.6173000000008</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="322"/>
-      <c r="C24" s="323"/>
-      <c r="D24" s="323"/>
-      <c r="E24" s="323"/>
-      <c r="F24" s="323"/>
-      <c r="G24" s="323"/>
-      <c r="H24" s="323"/>
-      <c r="I24" s="323"/>
-      <c r="J24" s="323"/>
-      <c r="K24" s="323"/>
-      <c r="L24" s="324"/>
+      <c r="B24" s="323"/>
+      <c r="C24" s="324"/>
+      <c r="D24" s="324"/>
+      <c r="E24" s="324"/>
+      <c r="F24" s="324"/>
+      <c r="G24" s="324"/>
+      <c r="H24" s="324"/>
+      <c r="I24" s="324"/>
+      <c r="J24" s="324"/>
+      <c r="K24" s="324"/>
+      <c r="L24" s="325"/>
       <c r="M24" s="99"/>
       <c r="N24" s="138" t="s">
         <v>83</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="P24" s="140">
         <f>O24*P23</f>
-        <v>34.677676500000011</v>
+        <v>35.178086500000006</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -12890,22 +12890,22 @@
       <c r="O25" s="328"/>
       <c r="P25" s="272">
         <f>+P23+P24</f>
-        <v>6970.2129765000018</v>
+        <v>7070.7953865000009</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B26" s="121" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="312"/>
-      <c r="D26" s="312"/>
-      <c r="E26" s="312"/>
-      <c r="F26" s="312"/>
-      <c r="G26" s="312"/>
-      <c r="H26" s="312"/>
-      <c r="I26" s="313"/>
-      <c r="J26" s="314"/>
-      <c r="K26" s="315"/>
+      <c r="C26" s="313"/>
+      <c r="D26" s="313"/>
+      <c r="E26" s="313"/>
+      <c r="F26" s="313"/>
+      <c r="G26" s="313"/>
+      <c r="H26" s="313"/>
+      <c r="I26" s="314"/>
+      <c r="J26" s="315"/>
+      <c r="K26" s="316"/>
     </row>
     <row r="27" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="28" spans="1:16" x14ac:dyDescent="0.35">
@@ -12916,6 +12916,19 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="24">
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="E1:K2"/>
+    <mergeCell ref="C26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="B18:L24"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="N21:O21"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="A6:B7"/>
     <mergeCell ref="I6:I7"/>
@@ -12927,19 +12940,6 @@
     <mergeCell ref="N6:N7"/>
     <mergeCell ref="C6:C7"/>
     <mergeCell ref="E6:F6"/>
-    <mergeCell ref="C26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="B18:L24"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="E1:K2"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <dataValidations disablePrompts="1" count="1">
@@ -12976,28 +12976,28 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:18 16382:16383" ht="21" x14ac:dyDescent="0.5">
-      <c r="A2" s="352" t="s">
+      <c r="A2" s="335" t="s">
         <v>91</v>
       </c>
-      <c r="B2" s="352"/>
-      <c r="C2" s="352"/>
+      <c r="B2" s="335"/>
+      <c r="C2" s="335"/>
     </row>
     <row r="3" spans="1:18 16382:16383" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="308" t="s">
+      <c r="A3" s="331" t="s">
         <v>92</v>
       </c>
-      <c r="B3" s="308"/>
-      <c r="C3" s="308"/>
+      <c r="B3" s="331"/>
+      <c r="C3" s="331"/>
       <c r="F3" s="85"/>
       <c r="G3" s="1"/>
-      <c r="J3" s="310" t="s">
+      <c r="J3" s="333" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="310"/>
-      <c r="L3" s="310"/>
-      <c r="M3" s="308"/>
-      <c r="N3" s="308"/>
-      <c r="O3" s="308"/>
+      <c r="K3" s="333"/>
+      <c r="L3" s="333"/>
+      <c r="M3" s="331"/>
+      <c r="N3" s="331"/>
+      <c r="O3" s="331"/>
       <c r="Q3" s="85"/>
       <c r="R3" s="1"/>
       <c r="XFB3" t="s">
@@ -13008,24 +13008,24 @@
       </c>
     </row>
     <row r="4" spans="1:18 16382:16383" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="308" t="s">
+      <c r="A4" s="331" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="308"/>
-      <c r="C4" s="308"/>
+      <c r="B4" s="331"/>
+      <c r="C4" s="331"/>
       <c r="F4" s="85"/>
       <c r="G4" s="1"/>
-      <c r="J4" s="310" t="s">
+      <c r="J4" s="333" t="s">
         <v>44</v>
       </c>
-      <c r="K4" s="310"/>
-      <c r="L4" s="310"/>
-      <c r="M4" s="351">
+      <c r="K4" s="333"/>
+      <c r="L4" s="333"/>
+      <c r="M4" s="336">
         <f ca="1">TODAY()+1</f>
-        <v>46267</v>
-      </c>
-      <c r="N4" s="351"/>
-      <c r="O4" s="351"/>
+        <v>46282</v>
+      </c>
+      <c r="N4" s="336"/>
+      <c r="O4" s="336"/>
       <c r="Q4" s="85"/>
       <c r="R4" s="1"/>
       <c r="XFB4" s="87" t="s">
@@ -13036,45 +13036,45 @@
       </c>
     </row>
     <row r="5" spans="1:18 16382:16383" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="350" t="s">
+      <c r="A5" s="337" t="s">
         <v>93</v>
       </c>
-      <c r="B5" s="350"/>
-      <c r="C5" s="350"/>
+      <c r="B5" s="337"/>
+      <c r="C5" s="337"/>
       <c r="F5" s="85"/>
       <c r="G5" s="1"/>
-      <c r="J5" s="310" t="s">
+      <c r="J5" s="333" t="s">
         <v>45</v>
       </c>
-      <c r="K5" s="310"/>
-      <c r="L5" s="310"/>
-      <c r="M5" s="351">
+      <c r="K5" s="333"/>
+      <c r="L5" s="333"/>
+      <c r="M5" s="336">
         <f ca="1">M4-1</f>
-        <v>46266</v>
-      </c>
-      <c r="N5" s="308"/>
-      <c r="O5" s="308"/>
+        <v>46281</v>
+      </c>
+      <c r="N5" s="331"/>
+      <c r="O5" s="331"/>
       <c r="Q5" s="85"/>
       <c r="R5" s="1"/>
     </row>
     <row r="6" spans="1:18 16382:16383" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="310" t="s">
+      <c r="A6" s="333" t="s">
         <v>94</v>
       </c>
-      <c r="B6" s="310"/>
-      <c r="C6" s="310"/>
+      <c r="B6" s="333"/>
+      <c r="C6" s="333"/>
       <c r="F6" s="85"/>
       <c r="G6" s="86"/>
-      <c r="J6" s="310" t="s">
+      <c r="J6" s="333" t="s">
         <v>69</v>
       </c>
-      <c r="K6" s="310"/>
-      <c r="L6" s="310"/>
-      <c r="M6" s="309" t="s">
+      <c r="K6" s="333"/>
+      <c r="L6" s="333"/>
+      <c r="M6" s="332" t="s">
         <v>62</v>
       </c>
-      <c r="N6" s="309"/>
-      <c r="O6" s="309"/>
+      <c r="N6" s="332"/>
+      <c r="O6" s="332"/>
       <c r="Q6" s="85"/>
       <c r="R6" s="86"/>
       <c r="XFB6" t="s">
@@ -13085,23 +13085,23 @@
       </c>
     </row>
     <row r="7" spans="1:18 16382:16383" s="87" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="310" t="s">
+      <c r="A7" s="333" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="310"/>
-      <c r="C7" s="310"/>
+      <c r="B7" s="333"/>
+      <c r="C7" s="333"/>
       <c r="F7" s="85"/>
       <c r="G7" s="86"/>
-      <c r="J7" s="310" t="s">
+      <c r="J7" s="333" t="s">
         <v>66</v>
       </c>
-      <c r="K7" s="310"/>
-      <c r="L7" s="310"/>
-      <c r="M7" s="309" t="s">
+      <c r="K7" s="333"/>
+      <c r="L7" s="333"/>
+      <c r="M7" s="332" t="s">
         <v>70</v>
       </c>
-      <c r="N7" s="309"/>
-      <c r="O7" s="309"/>
+      <c r="N7" s="332"/>
+      <c r="O7" s="332"/>
       <c r="Q7" s="85"/>
       <c r="R7" s="86"/>
       <c r="XFB7" t="s">
@@ -13112,44 +13112,44 @@
       </c>
     </row>
     <row r="8" spans="1:18 16382:16383" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="349" t="s">
+      <c r="A8" s="338" t="s">
         <v>95</v>
       </c>
-      <c r="B8" s="349"/>
-      <c r="C8" s="349"/>
+      <c r="B8" s="338"/>
+      <c r="C8" s="338"/>
       <c r="F8" s="85"/>
       <c r="G8" s="86"/>
-      <c r="J8" s="310" t="s">
+      <c r="J8" s="333" t="s">
         <v>67</v>
       </c>
-      <c r="K8" s="310"/>
-      <c r="L8" s="310"/>
-      <c r="M8" s="309" t="s">
+      <c r="K8" s="333"/>
+      <c r="L8" s="333"/>
+      <c r="M8" s="332" t="s">
         <v>71</v>
       </c>
-      <c r="N8" s="309"/>
-      <c r="O8" s="309"/>
+      <c r="N8" s="332"/>
+      <c r="O8" s="332"/>
       <c r="Q8" s="85"/>
       <c r="R8" s="86"/>
     </row>
     <row r="9" spans="1:18 16382:16383" x14ac:dyDescent="0.35">
-      <c r="A9" s="349" t="s">
+      <c r="A9" s="338" t="s">
         <v>96</v>
       </c>
-      <c r="B9" s="349"/>
-      <c r="C9" s="349"/>
+      <c r="B9" s="338"/>
+      <c r="C9" s="338"/>
       <c r="F9" s="85"/>
       <c r="G9" s="86"/>
-      <c r="J9" s="310" t="s">
+      <c r="J9" s="333" t="s">
         <v>68</v>
       </c>
-      <c r="K9" s="310"/>
-      <c r="L9" s="310"/>
-      <c r="M9" s="309" t="s">
+      <c r="K9" s="333"/>
+      <c r="L9" s="333"/>
+      <c r="M9" s="332" t="s">
         <v>104</v>
       </c>
-      <c r="N9" s="309"/>
-      <c r="O9" s="309"/>
+      <c r="N9" s="332"/>
+      <c r="O9" s="332"/>
       <c r="Q9" s="85"/>
       <c r="R9" s="86"/>
       <c r="XFC9" t="s">
@@ -13157,23 +13157,23 @@
       </c>
     </row>
     <row r="10" spans="1:18 16382:16383" x14ac:dyDescent="0.35">
-      <c r="A10" s="349" t="s">
+      <c r="A10" s="338" t="s">
         <v>97</v>
       </c>
-      <c r="B10" s="349"/>
-      <c r="C10" s="349"/>
+      <c r="B10" s="338"/>
+      <c r="C10" s="338"/>
       <c r="F10" s="85"/>
       <c r="G10" s="1"/>
-      <c r="J10" s="310" t="s">
+      <c r="J10" s="333" t="s">
         <v>46</v>
       </c>
-      <c r="K10" s="310"/>
-      <c r="L10" s="310"/>
-      <c r="M10" s="308" t="s">
+      <c r="K10" s="333"/>
+      <c r="L10" s="333"/>
+      <c r="M10" s="331" t="s">
         <v>47</v>
       </c>
-      <c r="N10" s="308"/>
-      <c r="O10" s="308"/>
+      <c r="N10" s="331"/>
+      <c r="O10" s="331"/>
       <c r="Q10" s="85"/>
       <c r="R10" s="1"/>
       <c r="XFC10" t="s">
@@ -13193,16 +13193,16 @@
       </c>
       <c r="F11" s="85"/>
       <c r="G11" s="1"/>
-      <c r="J11" s="310" t="s">
+      <c r="J11" s="333" t="s">
         <v>48</v>
       </c>
-      <c r="K11" s="310"/>
-      <c r="L11" s="310"/>
-      <c r="M11" s="308" t="s">
+      <c r="K11" s="333"/>
+      <c r="L11" s="333"/>
+      <c r="M11" s="331" t="s">
         <v>49</v>
       </c>
-      <c r="N11" s="308"/>
-      <c r="O11" s="308"/>
+      <c r="N11" s="331"/>
+      <c r="O11" s="331"/>
       <c r="P11" s="249"/>
       <c r="Q11" s="85"/>
       <c r="R11" s="1"/>
@@ -13220,14 +13220,14 @@
       </c>
       <c r="F12" s="85"/>
       <c r="G12" s="1"/>
-      <c r="J12" s="310" t="s">
+      <c r="J12" s="333" t="s">
         <v>50</v>
       </c>
-      <c r="K12" s="310"/>
-      <c r="L12" s="310"/>
-      <c r="M12" s="308"/>
-      <c r="N12" s="308"/>
-      <c r="O12" s="308"/>
+      <c r="K12" s="333"/>
+      <c r="L12" s="333"/>
+      <c r="M12" s="331"/>
+      <c r="N12" s="331"/>
+      <c r="O12" s="331"/>
       <c r="Q12" s="85"/>
       <c r="R12" s="1"/>
       <c r="XFC12" t="s">
@@ -13244,11 +13244,11 @@
       </c>
     </row>
     <row r="14" spans="1:18 16382:16383" ht="20.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="340" t="s">
+      <c r="A14" s="339" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="341"/>
-      <c r="C14" s="344" t="s">
+      <c r="B14" s="340"/>
+      <c r="C14" s="343" t="s">
         <v>90</v>
       </c>
       <c r="D14" s="88" t="s">
@@ -13260,17 +13260,17 @@
       <c r="F14" s="115" t="s">
         <v>53</v>
       </c>
-      <c r="G14" s="346" t="s">
+      <c r="G14" s="345" t="s">
         <v>54</v>
       </c>
-      <c r="H14" s="336"/>
+      <c r="H14" s="346"/>
       <c r="I14" s="347" t="s">
         <v>77</v>
       </c>
-      <c r="J14" s="335" t="s">
+      <c r="J14" s="349" t="s">
         <v>55</v>
       </c>
-      <c r="K14" s="336"/>
+      <c r="K14" s="346"/>
       <c r="L14" s="347" t="s">
         <v>84</v>
       </c>
@@ -13288,9 +13288,9 @@
       </c>
     </row>
     <row r="15" spans="1:18 16382:16383" ht="20.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="342"/>
-      <c r="B15" s="343"/>
-      <c r="C15" s="345"/>
+      <c r="A15" s="341"/>
+      <c r="B15" s="342"/>
+      <c r="C15" s="344"/>
       <c r="D15" s="90" t="s">
         <v>57</v>
       </c>
@@ -13835,17 +13835,17 @@
       </c>
     </row>
     <row r="25" spans="1:18 16383:16383" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="337">
+      <c r="A25" s="350">
         <f>COUNT(A16:A24)</f>
         <v>0</v>
       </c>
-      <c r="B25" s="338"/>
-      <c r="C25" s="338" t="s">
+      <c r="B25" s="351"/>
+      <c r="C25" s="351" t="s">
         <v>40</v>
       </c>
-      <c r="D25" s="338"/>
-      <c r="E25" s="338"/>
-      <c r="F25" s="339"/>
+      <c r="D25" s="351"/>
+      <c r="E25" s="351"/>
+      <c r="F25" s="352"/>
       <c r="G25" s="117">
         <f t="shared" ref="G25:L25" si="7">SUM(G16:G24)</f>
         <v>0</v>
@@ -13911,99 +13911,99 @@
       <c r="H27" s="94"/>
     </row>
     <row r="28" spans="1:18 16383:16383" x14ac:dyDescent="0.35">
-      <c r="B28" s="316" t="s">
+      <c r="B28" s="317" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="317"/>
-      <c r="D28" s="317"/>
-      <c r="E28" s="317"/>
-      <c r="F28" s="317"/>
-      <c r="G28" s="317"/>
-      <c r="H28" s="317"/>
-      <c r="I28" s="317"/>
-      <c r="J28" s="317"/>
-      <c r="K28" s="318"/>
-      <c r="M28" s="330" t="s">
+      <c r="C28" s="318"/>
+      <c r="D28" s="318"/>
+      <c r="E28" s="318"/>
+      <c r="F28" s="318"/>
+      <c r="G28" s="318"/>
+      <c r="H28" s="318"/>
+      <c r="I28" s="318"/>
+      <c r="J28" s="318"/>
+      <c r="K28" s="319"/>
+      <c r="M28" s="309" t="s">
         <v>60</v>
       </c>
-      <c r="N28" s="331"/>
+      <c r="N28" s="310"/>
       <c r="O28" s="139">
         <f>I25</f>
         <v>1452.8</v>
       </c>
     </row>
     <row r="29" spans="1:18 16383:16383" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="319"/>
-      <c r="C29" s="320"/>
-      <c r="D29" s="320"/>
-      <c r="E29" s="320"/>
-      <c r="F29" s="320"/>
-      <c r="G29" s="320"/>
-      <c r="H29" s="320"/>
-      <c r="I29" s="320"/>
-      <c r="J29" s="320"/>
-      <c r="K29" s="321"/>
-      <c r="M29" s="325" t="s">
+      <c r="B29" s="320"/>
+      <c r="C29" s="321"/>
+      <c r="D29" s="321"/>
+      <c r="E29" s="321"/>
+      <c r="F29" s="321"/>
+      <c r="G29" s="321"/>
+      <c r="H29" s="321"/>
+      <c r="I29" s="321"/>
+      <c r="J29" s="321"/>
+      <c r="K29" s="322"/>
+      <c r="M29" s="326" t="s">
         <v>85</v>
       </c>
-      <c r="N29" s="326"/>
+      <c r="N29" s="311"/>
       <c r="O29" s="140">
         <f>K25</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:18 16383:16383" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="319"/>
-      <c r="C30" s="320"/>
-      <c r="D30" s="320"/>
-      <c r="E30" s="320"/>
-      <c r="F30" s="320"/>
-      <c r="G30" s="320"/>
-      <c r="H30" s="320"/>
-      <c r="I30" s="320"/>
-      <c r="J30" s="320"/>
-      <c r="K30" s="321"/>
-      <c r="M30" s="325" t="s">
+      <c r="B30" s="320"/>
+      <c r="C30" s="321"/>
+      <c r="D30" s="321"/>
+      <c r="E30" s="321"/>
+      <c r="F30" s="321"/>
+      <c r="G30" s="321"/>
+      <c r="H30" s="321"/>
+      <c r="I30" s="321"/>
+      <c r="J30" s="321"/>
+      <c r="K30" s="322"/>
+      <c r="M30" s="326" t="s">
         <v>86</v>
       </c>
-      <c r="N30" s="326"/>
+      <c r="N30" s="311"/>
       <c r="O30" s="140">
         <f>J25</f>
         <v>50.848000000000006</v>
       </c>
     </row>
     <row r="31" spans="1:18 16383:16383" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="319"/>
-      <c r="C31" s="320"/>
-      <c r="D31" s="320"/>
-      <c r="E31" s="320"/>
-      <c r="F31" s="320"/>
-      <c r="G31" s="320"/>
-      <c r="H31" s="320"/>
-      <c r="I31" s="320"/>
-      <c r="J31" s="320"/>
-      <c r="K31" s="321"/>
+      <c r="B31" s="320"/>
+      <c r="C31" s="321"/>
+      <c r="D31" s="321"/>
+      <c r="E31" s="321"/>
+      <c r="F31" s="321"/>
+      <c r="G31" s="321"/>
+      <c r="H31" s="321"/>
+      <c r="I31" s="321"/>
+      <c r="J31" s="321"/>
+      <c r="K31" s="322"/>
       <c r="L31" s="131"/>
-      <c r="M31" s="325" t="s">
+      <c r="M31" s="326" t="s">
         <v>87</v>
       </c>
-      <c r="N31" s="326"/>
+      <c r="N31" s="311"/>
       <c r="O31" s="140">
         <f>O28-O29-O30</f>
         <v>1401.952</v>
       </c>
     </row>
     <row r="32" spans="1:18 16383:16383" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="319"/>
-      <c r="C32" s="320"/>
-      <c r="D32" s="320"/>
-      <c r="E32" s="320"/>
-      <c r="F32" s="320"/>
-      <c r="G32" s="320"/>
-      <c r="H32" s="320"/>
-      <c r="I32" s="320"/>
-      <c r="J32" s="320"/>
-      <c r="K32" s="321"/>
+      <c r="B32" s="320"/>
+      <c r="C32" s="321"/>
+      <c r="D32" s="321"/>
+      <c r="E32" s="321"/>
+      <c r="F32" s="321"/>
+      <c r="G32" s="321"/>
+      <c r="H32" s="321"/>
+      <c r="I32" s="321"/>
+      <c r="J32" s="321"/>
+      <c r="K32" s="322"/>
       <c r="L32" s="131"/>
       <c r="M32" s="136" t="s">
         <v>61</v>
@@ -14018,37 +14018,37 @@
       </c>
     </row>
     <row r="33" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="319"/>
-      <c r="C33" s="320"/>
-      <c r="D33" s="320"/>
-      <c r="E33" s="320"/>
-      <c r="F33" s="320"/>
-      <c r="G33" s="320"/>
-      <c r="H33" s="320"/>
-      <c r="I33" s="320"/>
-      <c r="J33" s="320"/>
-      <c r="K33" s="321"/>
+      <c r="B33" s="320"/>
+      <c r="C33" s="321"/>
+      <c r="D33" s="321"/>
+      <c r="E33" s="321"/>
+      <c r="F33" s="321"/>
+      <c r="G33" s="321"/>
+      <c r="H33" s="321"/>
+      <c r="I33" s="321"/>
+      <c r="J33" s="321"/>
+      <c r="K33" s="322"/>
       <c r="L33" s="131"/>
-      <c r="M33" s="332" t="s">
+      <c r="M33" s="329" t="s">
         <v>76</v>
       </c>
-      <c r="N33" s="333"/>
+      <c r="N33" s="330"/>
       <c r="O33" s="140">
         <f>O31+O32</f>
         <v>1710.3814400000001</v>
       </c>
     </row>
     <row r="34" spans="2:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="322"/>
-      <c r="C34" s="323"/>
-      <c r="D34" s="323"/>
-      <c r="E34" s="323"/>
-      <c r="F34" s="323"/>
-      <c r="G34" s="323"/>
-      <c r="H34" s="323"/>
-      <c r="I34" s="323"/>
-      <c r="J34" s="323"/>
-      <c r="K34" s="324"/>
+      <c r="B34" s="323"/>
+      <c r="C34" s="324"/>
+      <c r="D34" s="324"/>
+      <c r="E34" s="324"/>
+      <c r="F34" s="324"/>
+      <c r="G34" s="324"/>
+      <c r="H34" s="324"/>
+      <c r="I34" s="324"/>
+      <c r="J34" s="324"/>
+      <c r="K34" s="325"/>
       <c r="L34" s="99"/>
       <c r="M34" s="138" t="s">
         <v>83</v>
@@ -14076,53 +14076,19 @@
       <c r="B36" s="121" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="312"/>
-      <c r="D36" s="312"/>
-      <c r="E36" s="312"/>
-      <c r="F36" s="312"/>
-      <c r="G36" s="312"/>
-      <c r="H36" s="312"/>
-      <c r="I36" s="313"/>
+      <c r="C36" s="313"/>
+      <c r="D36" s="313"/>
+      <c r="E36" s="313"/>
+      <c r="F36" s="313"/>
+      <c r="G36" s="313"/>
+      <c r="H36" s="313"/>
+      <c r="I36" s="314"/>
       <c r="J36" s="260"/>
     </row>
     <row r="37" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="45">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="M4:O4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="M5:O5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="M6:O6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="M7:O7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="M9:O9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="M10:O10"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="J12:L12"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="L14:L15"/>
     <mergeCell ref="M35:N35"/>
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="J14:K14"/>
@@ -14134,6 +14100,40 @@
     <mergeCell ref="M30:N30"/>
     <mergeCell ref="M31:N31"/>
     <mergeCell ref="M33:N33"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="J12:L12"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="M10:O10"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="M7:O7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="M5:O5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="M6:O6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="M4:O4"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M9:O9" xr:uid="{00000000-0002-0000-2200-000000000000}">
@@ -14187,7 +14187,7 @@
       <c r="C1" s="300" t="s">
         <v>438</v>
       </c>
-      <c r="D1" s="356" t="s">
+      <c r="D1" s="355" t="s">
         <v>439</v>
       </c>
       <c r="E1" s="300" t="s">
@@ -14198,23 +14198,23 @@
         <v>440</v>
       </c>
       <c r="H1" s="301"/>
-      <c r="I1" s="357" t="s">
+      <c r="I1" s="362" t="s">
         <v>441</v>
       </c>
-      <c r="J1" s="357"/>
-      <c r="K1" s="357" t="s">
+      <c r="J1" s="362"/>
+      <c r="K1" s="362" t="s">
         <v>442</v>
       </c>
-      <c r="L1" s="357"/>
-      <c r="M1" s="353" t="s">
+      <c r="L1" s="362"/>
+      <c r="M1" s="357" t="s">
         <v>484</v>
       </c>
-      <c r="N1" s="354"/>
-      <c r="O1" s="355"/>
+      <c r="N1" s="358"/>
+      <c r="O1" s="359"/>
     </row>
     <row r="2" spans="3:24" ht="29" x14ac:dyDescent="0.35">
       <c r="C2" s="300"/>
-      <c r="D2" s="356"/>
+      <c r="D2" s="355"/>
       <c r="E2" s="168" t="s">
         <v>36</v>
       </c>
@@ -14388,13 +14388,13 @@
       </c>
     </row>
     <row r="6" spans="3:24" x14ac:dyDescent="0.35">
-      <c r="C6" s="358" t="s">
+      <c r="C6" s="360" t="s">
         <v>476</v>
       </c>
-      <c r="D6" s="358"/>
-      <c r="E6" s="358"/>
-      <c r="F6" s="358"/>
-      <c r="G6" s="358"/>
+      <c r="D6" s="360"/>
+      <c r="E6" s="360"/>
+      <c r="F6" s="360"/>
+      <c r="G6" s="360"/>
       <c r="T6" s="256" t="s">
         <v>487</v>
       </c>
@@ -14409,11 +14409,11 @@
       <c r="D7" s="299" t="s">
         <v>439</v>
       </c>
-      <c r="E7" s="360" t="s">
+      <c r="E7" s="356" t="s">
         <v>58</v>
       </c>
-      <c r="F7" s="360"/>
-      <c r="G7" s="361" t="s">
+      <c r="F7" s="356"/>
+      <c r="G7" s="354" t="s">
         <v>440</v>
       </c>
       <c r="H7" s="301"/>
@@ -14425,27 +14425,27 @@
         <v>442</v>
       </c>
       <c r="L7" s="303"/>
-      <c r="M7" s="353" t="s">
+      <c r="M7" s="357" t="s">
         <v>484</v>
       </c>
-      <c r="N7" s="354"/>
-      <c r="O7" s="355"/>
+      <c r="N7" s="358"/>
+      <c r="O7" s="359"/>
       <c r="P7" s="255" t="s">
         <v>475</v>
       </c>
       <c r="Q7" s="242" t="s">
         <v>473</v>
       </c>
-      <c r="R7" s="356" t="s">
+      <c r="R7" s="355" t="s">
         <v>475</v>
       </c>
-      <c r="S7" s="356" t="s">
+      <c r="S7" s="355" t="s">
         <v>485</v>
       </c>
-      <c r="T7" s="362" t="s">
+      <c r="T7" s="353" t="s">
         <v>486</v>
       </c>
-      <c r="U7" s="362" t="s">
+      <c r="U7" s="353" t="s">
         <v>486</v>
       </c>
     </row>
@@ -14491,10 +14491,10 @@
       <c r="Q8" s="242" t="s">
         <v>474</v>
       </c>
-      <c r="R8" s="356"/>
-      <c r="S8" s="356"/>
-      <c r="T8" s="361"/>
-      <c r="U8" s="361"/>
+      <c r="R8" s="355"/>
+      <c r="S8" s="355"/>
+      <c r="T8" s="354"/>
+      <c r="U8" s="354"/>
     </row>
     <row r="9" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C9" s="166" t="s">
@@ -14701,13 +14701,13 @@
       </c>
     </row>
     <row r="12" spans="3:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C12" s="359" t="s">
+      <c r="C12" s="361" t="s">
         <v>477</v>
       </c>
-      <c r="D12" s="359"/>
-      <c r="E12" s="359"/>
-      <c r="F12" s="359"/>
-      <c r="G12" s="359"/>
+      <c r="D12" s="361"/>
+      <c r="E12" s="361"/>
+      <c r="F12" s="361"/>
+      <c r="G12" s="361"/>
     </row>
     <row r="13" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C13" s="296" t="s">
@@ -14732,27 +14732,27 @@
         <v>442</v>
       </c>
       <c r="L13" s="303"/>
-      <c r="M13" s="353" t="s">
+      <c r="M13" s="357" t="s">
         <v>484</v>
       </c>
-      <c r="N13" s="354"/>
-      <c r="O13" s="355"/>
+      <c r="N13" s="358"/>
+      <c r="O13" s="359"/>
       <c r="P13" s="255" t="s">
         <v>475</v>
       </c>
       <c r="Q13" s="242" t="s">
         <v>473</v>
       </c>
-      <c r="R13" s="356" t="s">
+      <c r="R13" s="355" t="s">
         <v>475</v>
       </c>
-      <c r="S13" s="356" t="s">
+      <c r="S13" s="355" t="s">
         <v>485</v>
       </c>
-      <c r="T13" s="362" t="s">
+      <c r="T13" s="353" t="s">
         <v>486</v>
       </c>
-      <c r="U13" s="362" t="s">
+      <c r="U13" s="353" t="s">
         <v>486</v>
       </c>
     </row>
@@ -14798,10 +14798,10 @@
       <c r="Q14" s="242" t="s">
         <v>474</v>
       </c>
-      <c r="R14" s="356"/>
-      <c r="S14" s="356"/>
-      <c r="T14" s="361"/>
-      <c r="U14" s="361"/>
+      <c r="R14" s="355"/>
+      <c r="S14" s="355"/>
+      <c r="T14" s="354"/>
+      <c r="U14" s="354"/>
     </row>
     <row r="15" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C15" s="166" t="s">
@@ -15008,13 +15008,13 @@
       </c>
     </row>
     <row r="19" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C19" s="358" t="s">
+      <c r="C19" s="360" t="s">
         <v>478</v>
       </c>
-      <c r="D19" s="358"/>
-      <c r="E19" s="358"/>
-      <c r="F19" s="358"/>
-      <c r="G19" s="358"/>
+      <c r="D19" s="360"/>
+      <c r="E19" s="360"/>
+      <c r="F19" s="360"/>
+      <c r="G19" s="360"/>
     </row>
     <row r="20" spans="3:21" x14ac:dyDescent="0.35">
       <c r="C20" s="296" t="s">
@@ -15039,27 +15039,27 @@
         <v>442</v>
       </c>
       <c r="L20" s="303"/>
-      <c r="M20" s="353" t="s">
+      <c r="M20" s="357" t="s">
         <v>484</v>
       </c>
-      <c r="N20" s="354"/>
-      <c r="O20" s="355"/>
+      <c r="N20" s="358"/>
+      <c r="O20" s="359"/>
       <c r="P20" s="255" t="s">
         <v>475</v>
       </c>
       <c r="Q20" s="242" t="s">
         <v>473</v>
       </c>
-      <c r="R20" s="356" t="s">
+      <c r="R20" s="355" t="s">
         <v>475</v>
       </c>
-      <c r="S20" s="356" t="s">
+      <c r="S20" s="355" t="s">
         <v>485</v>
       </c>
-      <c r="T20" s="362" t="s">
+      <c r="T20" s="353" t="s">
         <v>486</v>
       </c>
-      <c r="U20" s="362" t="s">
+      <c r="U20" s="353" t="s">
         <v>486</v>
       </c>
     </row>
@@ -15105,10 +15105,10 @@
       <c r="Q21" s="242" t="s">
         <v>474</v>
       </c>
-      <c r="R21" s="356"/>
-      <c r="S21" s="356"/>
-      <c r="T21" s="361"/>
-      <c r="U21" s="361"/>
+      <c r="R21" s="355"/>
+      <c r="S21" s="355"/>
+      <c r="T21" s="354"/>
+      <c r="U21" s="354"/>
     </row>
     <row r="22" spans="3:21" x14ac:dyDescent="0.35">
       <c r="C22" s="166" t="s">
@@ -15333,13 +15333,13 @@
       <c r="R25" s="164"/>
     </row>
     <row r="26" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C26" s="358" t="s">
+      <c r="C26" s="360" t="s">
         <v>479</v>
       </c>
-      <c r="D26" s="358"/>
-      <c r="E26" s="358"/>
-      <c r="F26" s="358"/>
-      <c r="G26" s="358"/>
+      <c r="D26" s="360"/>
+      <c r="E26" s="360"/>
+      <c r="F26" s="360"/>
+      <c r="G26" s="360"/>
     </row>
     <row r="27" spans="3:21" x14ac:dyDescent="0.35">
       <c r="C27" s="296" t="s">
@@ -15364,27 +15364,27 @@
         <v>442</v>
       </c>
       <c r="L27" s="303"/>
-      <c r="M27" s="353" t="s">
+      <c r="M27" s="357" t="s">
         <v>484</v>
       </c>
-      <c r="N27" s="354"/>
-      <c r="O27" s="355"/>
+      <c r="N27" s="358"/>
+      <c r="O27" s="359"/>
       <c r="P27" s="255" t="s">
         <v>475</v>
       </c>
       <c r="Q27" s="242" t="s">
         <v>473</v>
       </c>
-      <c r="R27" s="356" t="s">
+      <c r="R27" s="355" t="s">
         <v>475</v>
       </c>
-      <c r="S27" s="356" t="s">
+      <c r="S27" s="355" t="s">
         <v>485</v>
       </c>
-      <c r="T27" s="362" t="s">
+      <c r="T27" s="353" t="s">
         <v>486</v>
       </c>
-      <c r="U27" s="362" t="s">
+      <c r="U27" s="353" t="s">
         <v>486</v>
       </c>
     </row>
@@ -15430,10 +15430,10 @@
       <c r="Q28" s="242" t="s">
         <v>474</v>
       </c>
-      <c r="R28" s="356"/>
-      <c r="S28" s="356"/>
-      <c r="T28" s="361"/>
-      <c r="U28" s="361"/>
+      <c r="R28" s="355"/>
+      <c r="S28" s="355"/>
+      <c r="T28" s="354"/>
+      <c r="U28" s="354"/>
     </row>
     <row r="29" spans="3:21" x14ac:dyDescent="0.35">
       <c r="C29" s="166" t="s">
@@ -15641,29 +15641,22 @@
     </row>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="U20:U21"/>
-    <mergeCell ref="S27:S28"/>
-    <mergeCell ref="T27:T28"/>
-    <mergeCell ref="U27:U28"/>
-    <mergeCell ref="U7:U8"/>
-    <mergeCell ref="S13:S14"/>
-    <mergeCell ref="T13:T14"/>
-    <mergeCell ref="U13:U14"/>
-    <mergeCell ref="S7:S8"/>
-    <mergeCell ref="T7:T8"/>
-    <mergeCell ref="S20:S21"/>
-    <mergeCell ref="T20:T21"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="R27:R28"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="R7:R8"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="M7:O7"/>
+    <mergeCell ref="M13:O13"/>
+    <mergeCell ref="M20:O20"/>
+    <mergeCell ref="R20:R21"/>
+    <mergeCell ref="R13:R14"/>
     <mergeCell ref="M27:O27"/>
     <mergeCell ref="C19:G19"/>
     <mergeCell ref="C26:G26"/>
@@ -15680,22 +15673,29 @@
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="D13:D14"/>
     <mergeCell ref="E13:F13"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="R27:R28"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="R7:R8"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="M7:O7"/>
-    <mergeCell ref="M13:O13"/>
-    <mergeCell ref="M20:O20"/>
-    <mergeCell ref="R20:R21"/>
-    <mergeCell ref="R13:R14"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="U20:U21"/>
+    <mergeCell ref="S27:S28"/>
+    <mergeCell ref="T27:T28"/>
+    <mergeCell ref="U27:U28"/>
+    <mergeCell ref="U7:U8"/>
+    <mergeCell ref="S13:S14"/>
+    <mergeCell ref="T13:T14"/>
+    <mergeCell ref="U13:U14"/>
+    <mergeCell ref="S7:S8"/>
+    <mergeCell ref="T7:T8"/>
+    <mergeCell ref="S20:S21"/>
+    <mergeCell ref="T20:T21"/>
   </mergeCells>
   <conditionalFormatting sqref="C1 C3:C5">
     <cfRule type="cellIs" dxfId="44" priority="1" stopIfTrue="1" operator="lessThan">
@@ -15769,7 +15769,7 @@
       <c r="B1" s="300" t="s">
         <v>438</v>
       </c>
-      <c r="C1" s="356" t="s">
+      <c r="C1" s="355" t="s">
         <v>439</v>
       </c>
       <c r="D1" s="300" t="s">
@@ -15780,23 +15780,23 @@
         <v>440</v>
       </c>
       <c r="G1" s="301"/>
-      <c r="H1" s="357" t="s">
+      <c r="H1" s="362" t="s">
         <v>441</v>
       </c>
-      <c r="I1" s="357"/>
-      <c r="J1" s="357" t="s">
+      <c r="I1" s="362"/>
+      <c r="J1" s="362" t="s">
         <v>442</v>
       </c>
-      <c r="K1" s="357"/>
-      <c r="L1" s="353" t="s">
+      <c r="K1" s="362"/>
+      <c r="L1" s="357" t="s">
         <v>484</v>
       </c>
-      <c r="M1" s="354"/>
-      <c r="N1" s="355"/>
+      <c r="M1" s="358"/>
+      <c r="N1" s="359"/>
     </row>
     <row r="2" spans="2:17" ht="29" x14ac:dyDescent="0.35">
       <c r="B2" s="300"/>
-      <c r="C2" s="356"/>
+      <c r="C2" s="355"/>
       <c r="D2" s="168" t="s">
         <v>36</v>
       </c>
@@ -16051,7 +16051,7 @@
       <c r="E5" s="148" t="s">
         <v>123</v>
       </c>
-      <c r="F5" s="364" t="s">
+      <c r="F5" s="365" t="s">
         <v>124</v>
       </c>
       <c r="G5" s="149" t="s">
@@ -16768,7 +16768,7 @@
       <c r="E59" s="159" t="s">
         <v>192</v>
       </c>
-      <c r="F59" s="365" t="s">
+      <c r="F59" s="364" t="s">
         <v>193</v>
       </c>
       <c r="G59" s="160" t="s">
@@ -16782,7 +16782,7 @@
       <c r="E60" s="159" t="s">
         <v>192</v>
       </c>
-      <c r="F60" s="365"/>
+      <c r="F60" s="364"/>
       <c r="G60" s="160" t="s">
         <v>195</v>
       </c>
@@ -16794,7 +16794,7 @@
       <c r="E61" s="159" t="s">
         <v>192</v>
       </c>
-      <c r="F61" s="365"/>
+      <c r="F61" s="364"/>
       <c r="G61" s="160" t="s">
         <v>196</v>
       </c>
@@ -16806,7 +16806,7 @@
       <c r="E62" s="159" t="s">
         <v>192</v>
       </c>
-      <c r="F62" s="365"/>
+      <c r="F62" s="364"/>
       <c r="G62" s="160" t="s">
         <v>197</v>
       </c>
@@ -16818,7 +16818,7 @@
       <c r="E63" s="159" t="s">
         <v>192</v>
       </c>
-      <c r="F63" s="365"/>
+      <c r="F63" s="364"/>
       <c r="G63" s="160" t="s">
         <v>198</v>
       </c>
@@ -16830,7 +16830,7 @@
       <c r="E64" s="159" t="s">
         <v>192</v>
       </c>
-      <c r="F64" s="365"/>
+      <c r="F64" s="364"/>
       <c r="G64" s="162" t="s">
         <v>199</v>
       </c>
@@ -17508,7 +17508,7 @@
       <c r="E119" s="159" t="s">
         <v>269</v>
       </c>
-      <c r="F119" s="365" t="s">
+      <c r="F119" s="364" t="s">
         <v>270</v>
       </c>
       <c r="G119" s="160" t="s">
@@ -17522,7 +17522,7 @@
       <c r="E120" s="159" t="s">
         <v>269</v>
       </c>
-      <c r="F120" s="365"/>
+      <c r="F120" s="364"/>
       <c r="G120" s="160" t="s">
         <v>272</v>
       </c>
@@ -17534,7 +17534,7 @@
       <c r="E121" s="159" t="s">
         <v>269</v>
       </c>
-      <c r="F121" s="365"/>
+      <c r="F121" s="364"/>
       <c r="G121" s="160" t="s">
         <v>273</v>
       </c>
@@ -17546,7 +17546,7 @@
       <c r="E122" s="159" t="s">
         <v>269</v>
       </c>
-      <c r="F122" s="365"/>
+      <c r="F122" s="364"/>
       <c r="G122" s="160" t="s">
         <v>274</v>
       </c>
@@ -17558,7 +17558,7 @@
       <c r="E123" s="159" t="s">
         <v>269</v>
       </c>
-      <c r="F123" s="365"/>
+      <c r="F123" s="364"/>
       <c r="G123" s="160" t="s">
         <v>275</v>
       </c>
@@ -17570,7 +17570,7 @@
       <c r="E124" s="159" t="s">
         <v>269</v>
       </c>
-      <c r="F124" s="365"/>
+      <c r="F124" s="364"/>
       <c r="G124" s="162" t="s">
         <v>276</v>
       </c>
@@ -18988,7 +18988,7 @@
       <c r="E239" s="159" t="s">
         <v>428</v>
       </c>
-      <c r="F239" s="365" t="s">
+      <c r="F239" s="364" t="s">
         <v>429</v>
       </c>
       <c r="G239" s="160" t="s">
@@ -19002,7 +19002,7 @@
       <c r="E240" s="159" t="s">
         <v>428</v>
       </c>
-      <c r="F240" s="365"/>
+      <c r="F240" s="364"/>
       <c r="G240" s="160" t="s">
         <v>431</v>
       </c>
@@ -19014,7 +19014,7 @@
       <c r="E241" s="159" t="s">
         <v>428</v>
       </c>
-      <c r="F241" s="365"/>
+      <c r="F241" s="364"/>
       <c r="G241" s="160" t="s">
         <v>432</v>
       </c>
@@ -19026,7 +19026,7 @@
       <c r="E242" s="159" t="s">
         <v>428</v>
       </c>
-      <c r="F242" s="365"/>
+      <c r="F242" s="364"/>
       <c r="G242" s="160" t="s">
         <v>433</v>
       </c>
@@ -19038,7 +19038,7 @@
       <c r="E243" s="159" t="s">
         <v>428</v>
       </c>
-      <c r="F243" s="365"/>
+      <c r="F243" s="364"/>
       <c r="G243" s="160" t="s">
         <v>434</v>
       </c>
@@ -19050,7 +19050,7 @@
       <c r="E244" s="159" t="s">
         <v>428</v>
       </c>
-      <c r="F244" s="365"/>
+      <c r="F244" s="364"/>
       <c r="G244" s="162" t="s">
         <v>435</v>
       </c>
@@ -19060,16 +19060,24 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="F221:F226"/>
-    <mergeCell ref="F227:F232"/>
-    <mergeCell ref="F233:F238"/>
-    <mergeCell ref="F239:F244"/>
-    <mergeCell ref="F185:F190"/>
-    <mergeCell ref="F191:F196"/>
-    <mergeCell ref="F197:F202"/>
-    <mergeCell ref="F203:F208"/>
-    <mergeCell ref="F209:F214"/>
-    <mergeCell ref="F215:F220"/>
+    <mergeCell ref="F35:F40"/>
+    <mergeCell ref="F5:F10"/>
+    <mergeCell ref="F11:F16"/>
+    <mergeCell ref="F17:F22"/>
+    <mergeCell ref="F23:F28"/>
+    <mergeCell ref="F29:F34"/>
+    <mergeCell ref="F107:F112"/>
+    <mergeCell ref="F41:F46"/>
+    <mergeCell ref="F47:F52"/>
+    <mergeCell ref="F53:F58"/>
+    <mergeCell ref="F59:F64"/>
+    <mergeCell ref="F65:F70"/>
+    <mergeCell ref="F71:F76"/>
+    <mergeCell ref="F77:F82"/>
+    <mergeCell ref="F83:F88"/>
+    <mergeCell ref="F89:F94"/>
+    <mergeCell ref="F95:F100"/>
+    <mergeCell ref="F101:F106"/>
     <mergeCell ref="F179:F184"/>
     <mergeCell ref="F113:F118"/>
     <mergeCell ref="F119:F124"/>
@@ -19082,24 +19090,16 @@
     <mergeCell ref="F161:F166"/>
     <mergeCell ref="F167:F172"/>
     <mergeCell ref="F173:F178"/>
-    <mergeCell ref="F107:F112"/>
-    <mergeCell ref="F41:F46"/>
-    <mergeCell ref="F47:F52"/>
-    <mergeCell ref="F53:F58"/>
-    <mergeCell ref="F59:F64"/>
-    <mergeCell ref="F65:F70"/>
-    <mergeCell ref="F71:F76"/>
-    <mergeCell ref="F77:F82"/>
-    <mergeCell ref="F83:F88"/>
-    <mergeCell ref="F89:F94"/>
-    <mergeCell ref="F95:F100"/>
-    <mergeCell ref="F101:F106"/>
-    <mergeCell ref="F35:F40"/>
-    <mergeCell ref="F5:F10"/>
-    <mergeCell ref="F11:F16"/>
-    <mergeCell ref="F17:F22"/>
-    <mergeCell ref="F23:F28"/>
-    <mergeCell ref="F29:F34"/>
+    <mergeCell ref="F221:F226"/>
+    <mergeCell ref="F227:F232"/>
+    <mergeCell ref="F233:F238"/>
+    <mergeCell ref="F239:F244"/>
+    <mergeCell ref="F185:F190"/>
+    <mergeCell ref="F191:F196"/>
+    <mergeCell ref="F197:F202"/>
+    <mergeCell ref="F203:F208"/>
+    <mergeCell ref="F209:F214"/>
+    <mergeCell ref="F215:F220"/>
   </mergeCells>
   <conditionalFormatting sqref="G5:G12 G14:G16 G35:G41 G44:G58">
     <cfRule type="duplicateValues" dxfId="31" priority="30"/>
